--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333316</v>
+        <v>123333433</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>91575</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R2" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,6 +769,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333433</v>
+        <v>123333316</v>
       </c>
       <c r="B3" t="n">
-        <v>91572</v>
+        <v>97542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +807,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R3" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,11 +894,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -914,7 +914,7 @@
         <v>123333329</v>
       </c>
       <c r="B4" t="n">
-        <v>97323</v>
+        <v>97326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333433</v>
+        <v>123333329</v>
       </c>
       <c r="B2" t="n">
-        <v>91575</v>
+        <v>97328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>224364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R2" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,16 +762,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -794,7 +781,7 @@
         <v>123333316</v>
       </c>
       <c r="B3" t="n">
-        <v>97542</v>
+        <v>97544</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -911,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333329</v>
+        <v>123333433</v>
       </c>
       <c r="B4" t="n">
-        <v>97326</v>
+        <v>91577</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,34 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224364</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R4" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -998,6 +988,16 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333329</v>
+        <v>123333433</v>
       </c>
       <c r="B2" t="n">
-        <v>97328</v>
+        <v>91583</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224364</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R2" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,6 +765,16 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -778,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333316</v>
+        <v>123333329</v>
       </c>
       <c r="B3" t="n">
-        <v>97544</v>
+        <v>97334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,33 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>224364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -878,11 +879,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -898,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333433</v>
+        <v>123333316</v>
       </c>
       <c r="B4" t="n">
-        <v>91577</v>
+        <v>97549</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,37 +910,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R4" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,11 +997,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333316</v>
+        <v>123333433</v>
       </c>
       <c r="B2" t="n">
-        <v>97552</v>
+        <v>91603</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R2" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,6 +769,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333433</v>
+        <v>123333329</v>
       </c>
       <c r="B3" t="n">
-        <v>91586</v>
+        <v>97354</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +807,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>224364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R3" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -885,16 +878,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -911,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333329</v>
+        <v>123333316</v>
       </c>
       <c r="B4" t="n">
-        <v>97337</v>
+        <v>97569</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,21 +910,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224364</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -998,6 +993,11 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123333433</v>
       </c>
       <c r="B2" t="n">
-        <v>91603</v>
+        <v>91608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>123333329</v>
       </c>
       <c r="B3" t="n">
-        <v>97354</v>
+        <v>97371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>123333316</v>
       </c>
       <c r="B4" t="n">
-        <v>97569</v>
+        <v>97586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333433</v>
+        <v>123333329</v>
       </c>
       <c r="B2" t="n">
-        <v>91608</v>
+        <v>97373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>224364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R2" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -765,16 +762,6 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333329</v>
+        <v>123333316</v>
       </c>
       <c r="B3" t="n">
-        <v>97371</v>
+        <v>97588</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +794,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>224364</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -879,6 +878,11 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333316</v>
+        <v>123333433</v>
       </c>
       <c r="B4" t="n">
-        <v>97586</v>
+        <v>91610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,46 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R4" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,6 +992,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123333329</v>
       </c>
       <c r="B2" t="n">
-        <v>97373</v>
+        <v>96961</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
         <v>123333316</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333316</v>
+        <v>123333433</v>
       </c>
       <c r="B3" t="n">
-        <v>97163</v>
+        <v>91610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +794,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R3" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,6 +872,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333433</v>
+        <v>123333316</v>
       </c>
       <c r="B4" t="n">
-        <v>91610</v>
+        <v>97163</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,37 +910,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>220686</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R4" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,11 +997,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333433</v>
+        <v>123333316</v>
       </c>
       <c r="B3" t="n">
-        <v>91610</v>
+        <v>97163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,37 +794,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R3" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,11 +881,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -894,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333316</v>
+        <v>123333433</v>
       </c>
       <c r="B4" t="n">
-        <v>97163</v>
+        <v>91610</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,46 +914,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R4" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,6 +992,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333329</v>
+        <v>123333316</v>
       </c>
       <c r="B2" t="n">
-        <v>96961</v>
+        <v>97163</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224364</v>
+        <v>220686</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -763,6 +775,11 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -778,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333316</v>
+        <v>123333433</v>
       </c>
       <c r="B3" t="n">
-        <v>97163</v>
+        <v>91610</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,46 +811,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R3" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,6 +889,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -898,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123333433</v>
+        <v>123333329</v>
       </c>
       <c r="B4" t="n">
-        <v>91610</v>
+        <v>96961</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,37 +927,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>224364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R4" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,16 +998,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">

--- a/artfynd/A 3161-2025 artfynd.xlsx
+++ b/artfynd/A 3161-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123333316</v>
+        <v>123333433</v>
       </c>
       <c r="B2" t="n">
-        <v>97163</v>
+        <v>91610</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220686</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmsjön O om, Srm</t>
+          <t>St.Tallsjön V om, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583988</v>
+        <v>584117</v>
       </c>
       <c r="R2" t="n">
-        <v>6557277</v>
+        <v>6556939</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -778,6 +769,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123333433</v>
+        <v>123333316</v>
       </c>
       <c r="B3" t="n">
-        <v>91610</v>
+        <v>97163</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,37 +807,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>220686</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kambräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Blechnum spicant</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>St.Tallsjön V om, Srm</t>
+          <t>Holmsjön O om, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584117</v>
+        <v>583988</v>
       </c>
       <c r="R3" t="n">
-        <v>6556939</v>
+        <v>6557277</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,11 +894,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>På granlåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
